--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127499745</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127499759</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127499759</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127499759</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127499759</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2025 artfynd.xlsx
+++ b/artfynd/A 35798-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499639</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127499813</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
